--- a/artfynd/A 27727-2026 artfynd.xlsx
+++ b/artfynd/A 27727-2026 artfynd.xlsx
@@ -1603,7 +1603,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Therese Steiner, Per Arneborn</t>
+          <t>Per Arneborn, Therese Steiner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 27727-2026 artfynd.xlsx
+++ b/artfynd/A 27727-2026 artfynd.xlsx
@@ -1603,7 +1603,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Arneborn, Therese Steiner</t>
+          <t>Therese Steiner, Per Arneborn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 27727-2026 artfynd.xlsx
+++ b/artfynd/A 27727-2026 artfynd.xlsx
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Therese Steiner, Per Arneborn</t>
+          <t>Per Arneborn, Therese Steiner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 27727-2026 artfynd.xlsx
+++ b/artfynd/A 27727-2026 artfynd.xlsx
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Arneborn, Therese Steiner</t>
+          <t>Therese Steiner, Per Arneborn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 27727-2026 artfynd.xlsx
+++ b/artfynd/A 27727-2026 artfynd.xlsx
@@ -1135,7 +1135,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Therese Steiner, Per Arneborn</t>
+          <t>Per Arneborn, Therese Steiner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 27727-2026 artfynd.xlsx
+++ b/artfynd/A 27727-2026 artfynd.xlsx
@@ -1135,7 +1135,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Arneborn, Therese Steiner</t>
+          <t>Therese Steiner, Per Arneborn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 27727-2026 artfynd.xlsx
+++ b/artfynd/A 27727-2026 artfynd.xlsx
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Therese Steiner, Per Arneborn</t>
+          <t>Per Arneborn, Therese Steiner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 27727-2026 artfynd.xlsx
+++ b/artfynd/A 27727-2026 artfynd.xlsx
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Arneborn, Therese Steiner</t>
+          <t>Therese Steiner, Per Arneborn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 27727-2026 artfynd.xlsx
+++ b/artfynd/A 27727-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1964532</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135035032</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135038196</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135035826</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135036012</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,6 +1403,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135036187</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135036208</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1607,6 +1647,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135036261</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1724,6 +1769,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135036308</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1841,6 +1891,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135036409</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1958,6 +2013,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135036438</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2075,6 +2135,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135036654</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2192,6 +2257,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135035390</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2323,6 +2393,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135036509</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2439,6 +2514,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135037872</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2568,6 +2648,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135036710</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2689,8 +2774,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034851</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27727-2026 artfynd.xlsx
+++ b/artfynd/A 27727-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135035032</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>135038196</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>135035826</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>135036012</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>135036187</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>135036208</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>135036261</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>135036308</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>135036409</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>135036438</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>135036654</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>135035390</v>
       </c>
       <c r="B14" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>135036509</v>
       </c>
       <c r="B15" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>135037872</v>
       </c>
       <c r="B16" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>135036710</v>
       </c>
       <c r="B17" t="n">
-        <v>58812</v>
+        <v>58817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>135034851</v>
       </c>
       <c r="B18" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2026 artfynd.xlsx
+++ b/artfynd/A 27727-2026 artfynd.xlsx
@@ -2659,7 +2659,7 @@
         <v>135034851</v>
       </c>
       <c r="B18" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
